--- a/artfynd/A 13999-2024 artfynd.xlsx
+++ b/artfynd/A 13999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>93929236</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499356.7229687353</v>
+        <v>499357</v>
       </c>
       <c r="R2" t="n">
-        <v>7133427.842346134</v>
+        <v>7133428</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105312140</v>
+        <v>113679216</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499599.9500980513</v>
+        <v>499533</v>
       </c>
       <c r="R3" t="n">
-        <v>7133802.493720989</v>
+        <v>7133556</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +860,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -901,17 +871,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679217</v>
+        <v>113680626</v>
       </c>
       <c r="B4" t="n">
-        <v>80437</v>
+        <v>93296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499529</v>
+        <v>499460</v>
       </c>
       <c r="R4" t="n">
-        <v>7133559</v>
+        <v>7133614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +964,12 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Tomas Rask</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1014,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680626</v>
+        <v>105312140</v>
       </c>
       <c r="B5" t="n">
-        <v>93229</v>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,13 +1023,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499460</v>
+        <v>499600</v>
       </c>
       <c r="R5" t="n">
-        <v>7133614</v>
+        <v>7133802</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,12 +1070,12 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1109,21 +1083,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Susanne Wiik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113679216</v>
+        <v>113679217</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499533</v>
+        <v>499529</v>
       </c>
       <c r="R6" t="n">
-        <v>7133556</v>
+        <v>7133559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,6 +1189,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131734588</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilltjärnen Sydost, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>499476</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7133319</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 13999-2024 artfynd.xlsx
+++ b/artfynd/A 13999-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93929236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680626</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312140</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,8 +1324,21 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>